--- a/data.mn/public/datasets/infant-mortality-rate-national-en.xlsx
+++ b/data.mn/public/datasets/infant-mortality-rate-national-en.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B121"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1632,6 +1632,76 @@
         <v>13</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
